--- a/C7FF82EC-F412-4566-ACDE-4888751F70E0/src/assets/一級輔導匯入範本.xlsx
+++ b/C7FF82EC-F412-4566-ACDE-4888751F70E0/src/assets/一級輔導匯入範本.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\輔導\C7FF82EC-F412-4566-ACDE-4888751F70E0\src\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w1241\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F950265E-EDF0-4627-9230-46853EEF3FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22053AAB-73E7-4921-9457-2BBB0592D0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F223C809-454F-4447-9BC2-A7549CA6F6F8}"/>
   </bookViews>
@@ -20,10 +20,741 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>李可為</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{D88B7894-FC73-43B2-A77F-2E6A9707BB90}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>學生目前班級</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{18FD7970-3287-4026-9B45-3515DAE2EE88}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>學生座號</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{29DE3498-847A-486D-B69C-962C0B2573B1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>學生學號</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{BD288A48-5580-4F0C-96CE-F89B46508750}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>請選擇：一般、休學、延修</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A3E1C263-6F46-419D-93BF-107F7981006A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>學生年級:
+如：1、2、3、4、5、6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{787C068E-F1C3-43F9-81B6-B026197B7C24}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>晤談的學年度</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>如：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>113</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>114</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{CB03D4FC-D644-4FF4-9FA7-5C55ABC41602}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>晤談學期</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>格式：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{D5516792-AB76-4104-9502-4701015C24D8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>如：2026/09/02</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{73FB502B-F363-4C58-B6C4-38A6FF2FDFB7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>如：第一節、第二節、上午、下午</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{6CC699CA-289A-4ADA-8844-87FA2CE3144C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>請選擇：面談、電話、聯絡簿、其他</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{0BC1F13C-1D7A-4ACA-825F-497CD6492EB7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>請選擇：學生、教職員、家長、其他</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{960989A3-9DAF-4103-8F04-5C364A15BAC0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>教師姓名</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{3A6C9E93-3B1E-4147-AB62-8142606CA437}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>請選擇：是、否
+是否輔導資料開放給下一任班導師，以利銜接。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{F2FFD9EC-0AC2-4BA9-9E77-BB3BBD92C270}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>李可為</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>可填寫多個選項，請以半型逗號隔開。如：人際困擾</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>師生關係。
+際困擾、師生關係、家庭困擾、自我探索、情緒困擾、生活壓力、創傷反應、自我傷害、性別議題、脆弱家庭、兒少保議題、學習困擾、生涯輔導、偏差行為、網路沉迷、中離（輟）拒學、藥物濫用、精神疾患、其他</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
@@ -36,62 +767,63 @@
     <t>學號</t>
   </si>
   <si>
+    <t>年級</t>
+  </si>
+  <si>
+    <t>學年度</t>
+  </si>
+  <si>
+    <t>學期</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>晤談時間</t>
+  </si>
+  <si>
+    <t>方式</t>
+  </si>
+  <si>
+    <t>方式其他</t>
+  </si>
+  <si>
+    <t>對象</t>
+  </si>
+  <si>
+    <t>對象其他</t>
+  </si>
+  <si>
+    <t>記錄者</t>
+  </si>
+  <si>
+    <t>暱稱</t>
+  </si>
+  <si>
+    <t>公開</t>
+  </si>
+  <si>
+    <t>聯絡事項</t>
+  </si>
+  <si>
+    <t>輔導內容</t>
+  </si>
+  <si>
+    <t>類別</t>
+  </si>
+  <si>
+    <t>類別其他</t>
+  </si>
+  <si>
     <t>狀態</t>
-  </si>
-  <si>
-    <t>年級</t>
-  </si>
-  <si>
-    <t>學年度</t>
-  </si>
-  <si>
-    <t>學期</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>晤談時間</t>
-  </si>
-  <si>
-    <t>方式</t>
-  </si>
-  <si>
-    <t>方式其他</t>
-  </si>
-  <si>
-    <t>對象</t>
-  </si>
-  <si>
-    <t>對象其他</t>
-  </si>
-  <si>
-    <t>記錄者</t>
-  </si>
-  <si>
-    <t>暱稱</t>
-  </si>
-  <si>
-    <t>公開</t>
-  </si>
-  <si>
-    <t>聯絡事項</t>
-  </si>
-  <si>
-    <t>輔導內容</t>
-  </si>
-  <si>
-    <t>類別</t>
-  </si>
-  <si>
-    <t>類別其他</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -135,6 +867,34 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -165,7 +925,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -174,6 +934,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -488,9 +1251,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A37D970-4F43-49D3-B020-0050317A4FC0}">
-  <dimension ref="A1:U1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A37D970-4F43-49D3-B020-0050317A4FC0}">
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="19" max="19" width="5.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -503,60 +1269,85 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="H2" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S500" xr:uid="{DC6BF903-E96D-48C5-83EF-00CE5B2D2DAF}">
+      <formula1>"人際困擾,師生關係,家庭困擾,自我探索,情緒困擾,生活壓力,創傷反應,自我傷害,性別議題,脆弱家庭,兒少保議題,學習困擾,生涯輔導,偏差行為,網路沉迷,中離（輟）拒學,藥物濫用,精神疾患,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P500" xr:uid="{406B81EE-4C7F-4E24-BD4C-32EFC5082AAB}">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L500" xr:uid="{530C10B0-4802-448B-B4E3-A55A0972D8C0}">
+      <formula1>"學生,教職員,家長,專業人員,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J500" xr:uid="{C8D31F4C-927B-4B17-992D-2B1A41F4DDE4}">
+      <formula1>"面談,電話,聯絡簿,個別約談家長,會議,E-mail,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G500" xr:uid="{3226A8EB-A574-4AD7-959C-E1309E0ED150}">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D500" xr:uid="{837DEE52-C012-4DB8-A68E-59D054400396}">
+      <formula1>"一般,休學,延修"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>